--- a/architectures and decision enablers/architecture decision enabler/cloud-readiness-assessment/CRA_Calculator.xlsx
+++ b/architectures and decision enablers/architecture decision enabler/cloud-readiness-assessment/CRA_Calculator.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amitp\Documents\portfolio-repo\architectures and decision enablers\cloud-readiness-assessment-enabler\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Amit\eBooks\Interview Quick Rampup\Fractional Architect Consulting &amp; Freelancing\UPWORK &amp; TOPMATE FILES AND PRODUCTS\CLOUD_READINESS_ASSESSMENT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C83D744-6EBB-4747-855F-63AAE5297DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F18144B-C78F-48E0-BDF7-D5C5132A2D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6EA83798-0DD6-40E8-BDD9-53B4FEBFB21D}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="121">
   <si>
     <t>Perspective</t>
   </si>
@@ -1277,6 +1277,9 @@
   </si>
   <si>
     <t>Result</t>
+  </si>
+  <si>
+    <t>© 2026 Amit Kulkarni All rights reserved</t>
   </si>
 </sst>
 </file>
@@ -1286,7 +1289,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1345,6 +1348,14 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1366,16 +1377,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1397,21 +1405,58 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="39">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF5D6D7E"/>
@@ -1713,19 +1758,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i/>
@@ -2041,16 +2073,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.25</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.25</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.75</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.375</c:v>
+                  <c:v>2.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>3.125</c:v>
@@ -2904,11 +2936,11 @@
     <tableColumn id="1" xr3:uid="{F945049B-64A4-4551-A316-D230978FC3B4}" name="Perspective" dataDxfId="36"/>
     <tableColumn id="2" xr3:uid="{BF1EA979-E2A6-47BF-A72B-11727105CF50}" name="Description" dataDxfId="35"/>
     <tableColumn id="3" xr3:uid="{DA966BB2-80B6-4483-8B36-F7971E6C36BE}" name="Question" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{1238EB9F-FF0F-4600-849A-01A80173F12E}" name="User Response " dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{15B7F211-0F08-4363-97F1-77C49E8EAFE4}" name="Numeric Score" dataDxfId="32">
+    <tableColumn id="4" xr3:uid="{1238EB9F-FF0F-4600-849A-01A80173F12E}" name="User Response " dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{15B7F211-0F08-4363-97F1-77C49E8EAFE4}" name="Numeric Score" dataDxfId="2">
       <calculatedColumnFormula array="1">_xlfn.IFS(D2="A", 1, D2="B", 2, D2="C", 3, D2="D", 4, TRUE, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{828B735E-9B29-4C93-83F9-DAEA4EAD33B2}" name="Individual Capability Strategy" dataDxfId="31">
+    <tableColumn id="6" xr3:uid="{828B735E-9B29-4C93-83F9-DAEA4EAD33B2}" name="Individual Capability Strategy" dataDxfId="1">
       <calculatedColumnFormula array="1">_xlfn.IFS(
     E2=1, _xlfn.IFS(
         A2="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -2932,7 +2964,7 @@
     TRUE, ""
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{808532A8-6EC5-47EF-9982-F12555A06F75}" name="T-Shirt Sizing" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{808532A8-6EC5-47EF-9982-F12555A06F75}" name="T-Shirt Sizing" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3261,25 +3293,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>115</v>
       </c>
       <c r="H1" s="1"/>
@@ -3288,20 +3320,20 @@
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="16" cm="1">
+        <f t="array" ref="E2">_xlfn.IFS(D2="A", 1, D2="B", 2, D2="C", 3, D2="D", 4, TRUE, 0)</f>
         <v>4</v>
       </c>
-      <c r="E2" s="12" cm="1">
-        <f t="array" ref="E2">_xlfn.IFS(D2="A", 1, D2="B", 2, D2="C", 3, D2="D", 4, TRUE, 0)</f>
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="str" cm="1">
+      <c r="F2" s="17" t="str" cm="1">
         <f t="array" ref="F2">_xlfn.IFS(
     E2=1, _xlfn.IFS(
         A2="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -3324,10 +3356,10 @@
     ),
     TRUE, ""
 )</f>
-        <v>REPLATFORM / LIFT-AND-SHAPE</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>117</v>
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="H2" s="1"/>
     </row>
@@ -3335,20 +3367,20 @@
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="12" cm="1">
+      <c r="D3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="16" cm="1">
         <f t="array" ref="E3">_xlfn.IFS(D3="A", 1, D3="B", 2, D3="C", 3, D3="D", 4, TRUE, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="F3" s="1" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="F3" s="17" t="str" cm="1">
         <f t="array" ref="F3">_xlfn.IFS(
     E3=1, _xlfn.IFS(
         A3="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -3371,9 +3403,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
-      </c>
-      <c r="G3" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G3" s="15" t="s">
         <v>117</v>
       </c>
       <c r="H3" s="1"/>
@@ -3382,20 +3414,20 @@
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="16" cm="1">
+        <f t="array" ref="E4">_xlfn.IFS(D4="A", 1, D4="B", 2, D4="C", 3, D4="D", 4, TRUE, 0)</f>
         <v>4</v>
       </c>
-      <c r="E4" s="12" cm="1">
-        <f t="array" ref="E4">_xlfn.IFS(D4="A", 1, D4="B", 2, D4="C", 3, D4="D", 4, TRUE, 0)</f>
-        <v>3</v>
-      </c>
-      <c r="F4" s="1" t="str" cm="1">
+      <c r="F4" s="17" t="str" cm="1">
         <f t="array" ref="F4">_xlfn.IFS(
     E4=1, _xlfn.IFS(
         A4="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -3418,9 +3450,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REPLATFORM / LIFT-AND-SHAPE</v>
-      </c>
-      <c r="G4" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G4" s="15" t="s">
         <v>116</v>
       </c>
       <c r="H4" s="1"/>
@@ -3429,20 +3461,20 @@
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="16" cm="1">
+        <f t="array" ref="E5">_xlfn.IFS(D5="A", 1, D5="B", 2, D5="C", 3, D5="D", 4, TRUE, 0)</f>
         <v>4</v>
       </c>
-      <c r="E5" s="12" cm="1">
-        <f t="array" ref="E5">_xlfn.IFS(D5="A", 1, D5="B", 2, D5="C", 3, D5="D", 4, TRUE, 0)</f>
-        <v>3</v>
-      </c>
-      <c r="F5" s="1" t="str" cm="1">
+      <c r="F5" s="17" t="str" cm="1">
         <f t="array" ref="F5">_xlfn.IFS(
     E5=1, _xlfn.IFS(
         A5="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -3465,9 +3497,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REPLATFORM / LIFT-AND-SHAPE</v>
-      </c>
-      <c r="G5" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G5" s="15" t="s">
         <v>118</v>
       </c>
       <c r="H5" s="1"/>
@@ -3476,20 +3508,20 @@
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="12" cm="1">
+      <c r="D6" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="16" cm="1">
         <f t="array" ref="E6">_xlfn.IFS(D6="A", 1, D6="B", 2, D6="C", 3, D6="D", 4, TRUE, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="F6" s="1" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="F6" s="17" t="str" cm="1">
         <f t="array" ref="F6">_xlfn.IFS(
     E6=1, _xlfn.IFS(
         A6="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -3512,9 +3544,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
-      </c>
-      <c r="G6" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G6" s="15" t="s">
         <v>117</v>
       </c>
       <c r="H6" s="1"/>
@@ -3523,20 +3555,20 @@
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="12" cm="1">
+      <c r="D7" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="16" cm="1">
         <f t="array" ref="E7">_xlfn.IFS(D7="A", 1, D7="B", 2, D7="C", 3, D7="D", 4, TRUE, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="F7" s="1" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="F7" s="17" t="str" cm="1">
         <f t="array" ref="F7">_xlfn.IFS(
     E7=1, _xlfn.IFS(
         A7="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -3559,9 +3591,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
-      </c>
-      <c r="G7" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G7" s="15" t="s">
         <v>117</v>
       </c>
       <c r="H7" s="1"/>
@@ -3570,20 +3602,20 @@
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="12" cm="1">
+      <c r="D8" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="16" cm="1">
         <f t="array" ref="E8">_xlfn.IFS(D8="A", 1, D8="B", 2, D8="C", 3, D8="D", 4, TRUE, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="F8" s="17" t="str" cm="1">
         <f t="array" ref="F8">_xlfn.IFS(
     E8=1, _xlfn.IFS(
         A8="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -3606,9 +3638,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>RETAIN (Fatal System/Dependency Blocker)</v>
-      </c>
-      <c r="G8" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G8" s="15" t="s">
         <v>118</v>
       </c>
       <c r="H8" s="1"/>
@@ -3617,20 +3649,20 @@
       <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="12" cm="1">
+      <c r="D9" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="16" cm="1">
         <f t="array" ref="E9">_xlfn.IFS(D9="A", 1, D9="B", 2, D9="C", 3, D9="D", 4, TRUE, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="F9" s="1" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="F9" s="17" t="str" cm="1">
         <f t="array" ref="F9">_xlfn.IFS(
     E9=1, _xlfn.IFS(
         A9="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -3653,9 +3685,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
-      </c>
-      <c r="G9" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G9" s="15" t="s">
         <v>117</v>
       </c>
       <c r="H9" s="1"/>
@@ -3664,20 +3696,20 @@
       <c r="A10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="12" cm="1">
+      <c r="D10" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="16" cm="1">
         <f t="array" ref="E10">_xlfn.IFS(D10="A", 1, D10="B", 2, D10="C", 3, D10="D", 4, TRUE, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="17" t="str" cm="1">
         <f t="array" ref="F10">_xlfn.IFS(
     E10=1, _xlfn.IFS(
         A10="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -3700,9 +3732,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>RETAIN (Fatal System/Dependency Blocker)</v>
-      </c>
-      <c r="G10" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G10" s="15" t="s">
         <v>117</v>
       </c>
       <c r="H10" s="1"/>
@@ -3711,20 +3743,20 @@
       <c r="A11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="12" cm="1">
+      <c r="D11" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="16" cm="1">
         <f t="array" ref="E11">_xlfn.IFS(D11="A", 1, D11="B", 2, D11="C", 3, D11="D", 4, TRUE, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="F11" s="1" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="F11" s="17" t="str" cm="1">
         <f t="array" ref="F11">_xlfn.IFS(
     E11=1, _xlfn.IFS(
         A11="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -3747,9 +3779,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
-      </c>
-      <c r="G11" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G11" s="15" t="s">
         <v>117</v>
       </c>
       <c r="H11" s="1"/>
@@ -3758,20 +3790,20 @@
       <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="16" cm="1">
+        <f t="array" ref="E12">_xlfn.IFS(D12="A", 1, D12="B", 2, D12="C", 3, D12="D", 4, TRUE, 0)</f>
         <v>4</v>
       </c>
-      <c r="E12" s="12" cm="1">
-        <f t="array" ref="E12">_xlfn.IFS(D12="A", 1, D12="B", 2, D12="C", 3, D12="D", 4, TRUE, 0)</f>
-        <v>3</v>
-      </c>
-      <c r="F12" s="1" t="str" cm="1">
+      <c r="F12" s="17" t="str" cm="1">
         <f t="array" ref="F12">_xlfn.IFS(
     E12=1, _xlfn.IFS(
         A12="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -3794,9 +3826,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REPLATFORM / LIFT-AND-SHAPE</v>
-      </c>
-      <c r="G12" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G12" s="15" t="s">
         <v>117</v>
       </c>
       <c r="H12" s="1"/>
@@ -3805,20 +3837,20 @@
       <c r="A13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="16" cm="1">
+        <f t="array" ref="E13">_xlfn.IFS(D13="A", 1, D13="B", 2, D13="C", 3, D13="D", 4, TRUE, 0)</f>
         <v>4</v>
       </c>
-      <c r="E13" s="12" cm="1">
-        <f t="array" ref="E13">_xlfn.IFS(D13="A", 1, D13="B", 2, D13="C", 3, D13="D", 4, TRUE, 0)</f>
-        <v>3</v>
-      </c>
-      <c r="F13" s="1" t="str" cm="1">
+      <c r="F13" s="17" t="str" cm="1">
         <f t="array" ref="F13">_xlfn.IFS(
     E13=1, _xlfn.IFS(
         A13="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -3841,9 +3873,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REPLATFORM / LIFT-AND-SHAPE</v>
-      </c>
-      <c r="G13" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G13" s="15" t="s">
         <v>117</v>
       </c>
       <c r="H13" s="1"/>
@@ -3852,20 +3884,20 @@
       <c r="A14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="12" cm="1">
+      <c r="D14" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="16" cm="1">
         <f t="array" ref="E14">_xlfn.IFS(D14="A", 1, D14="B", 2, D14="C", 3, D14="D", 4, TRUE, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="F14" s="1" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="F14" s="17" t="str" cm="1">
         <f t="array" ref="F14">_xlfn.IFS(
     E14=1, _xlfn.IFS(
         A14="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -3888,9 +3920,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
-      </c>
-      <c r="G14" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G14" s="15" t="s">
         <v>118</v>
       </c>
       <c r="H14" s="1"/>
@@ -3899,20 +3931,20 @@
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="12" cm="1">
+      <c r="D15" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="16" cm="1">
         <f t="array" ref="E15">_xlfn.IFS(D15="A", 1, D15="B", 2, D15="C", 3, D15="D", 4, TRUE, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="F15" s="1" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="F15" s="17" t="str" cm="1">
         <f t="array" ref="F15">_xlfn.IFS(
     E15=1, _xlfn.IFS(
         A15="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -3935,9 +3967,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
-      </c>
-      <c r="G15" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G15" s="15" t="s">
         <v>116</v>
       </c>
       <c r="H15" s="1"/>
@@ -3946,20 +3978,20 @@
       <c r="A16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="12" cm="1">
+      <c r="D16" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="16" cm="1">
         <f t="array" ref="E16">_xlfn.IFS(D16="A", 1, D16="B", 2, D16="C", 3, D16="D", 4, TRUE, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="F16" s="1" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="F16" s="17" t="str" cm="1">
         <f t="array" ref="F16">_xlfn.IFS(
     E16=1, _xlfn.IFS(
         A16="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -3982,9 +4014,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
-      </c>
-      <c r="G16" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G16" s="15" t="s">
         <v>117</v>
       </c>
       <c r="H16" s="1"/>
@@ -3993,20 +4025,20 @@
       <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="18" cm="1">
+        <f t="array" ref="E17">_xlfn.IFS(D17="A", 1, D17="B", 2, D17="C", 3, D17="D", 4, TRUE, 0)</f>
         <v>4</v>
       </c>
-      <c r="E17" s="13" cm="1">
-        <f t="array" ref="E17">_xlfn.IFS(D17="A", 1, D17="B", 2, D17="C", 3, D17="D", 4, TRUE, 0)</f>
-        <v>3</v>
-      </c>
-      <c r="F17" s="1" t="str" cm="1">
+      <c r="F17" s="17" t="str" cm="1">
         <f t="array" ref="F17">_xlfn.IFS(
     E17=1, _xlfn.IFS(
         A17="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4029,9 +4061,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REPLATFORM / LIFT-AND-SHAPE</v>
-      </c>
-      <c r="G17" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G17" s="15" t="s">
         <v>117</v>
       </c>
       <c r="H17" s="1"/>
@@ -4040,20 +4072,20 @@
       <c r="A18" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="13" cm="1">
+      <c r="E18" s="18" cm="1">
         <f t="array" ref="E18">_xlfn.IFS(D18="A", 1, D18="B", 2, D18="C", 3, D18="D", 4, TRUE, 0)</f>
         <v>4</v>
       </c>
-      <c r="F18" s="1" t="str" cm="1">
+      <c r="F18" s="17" t="str" cm="1">
         <f t="array" ref="F18">_xlfn.IFS(
     E18=1, _xlfn.IFS(
         A18="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4078,7 +4110,7 @@
 )</f>
         <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="15" t="s">
         <v>117</v>
       </c>
       <c r="H18" s="1"/>
@@ -4087,20 +4119,20 @@
       <c r="A19" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="13" cm="1">
+      <c r="D19" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="18" cm="1">
         <f t="array" ref="E19">_xlfn.IFS(D19="A", 1, D19="B", 2, D19="C", 3, D19="D", 4, TRUE, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="F19" s="1" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="F19" s="17" t="str" cm="1">
         <f t="array" ref="F19">_xlfn.IFS(
     E19=1, _xlfn.IFS(
         A19="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4123,9 +4155,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
-      </c>
-      <c r="G19" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G19" s="15" t="s">
         <v>117</v>
       </c>
       <c r="H19" s="1"/>
@@ -4134,20 +4166,20 @@
       <c r="A20" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="13" cm="1">
+      <c r="D20" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="18" cm="1">
         <f t="array" ref="E20">_xlfn.IFS(D20="A", 1, D20="B", 2, D20="C", 3, D20="D", 4, TRUE, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="F20" s="1" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="F20" s="17" t="str" cm="1">
         <f t="array" ref="F20">_xlfn.IFS(
     E20=1, _xlfn.IFS(
         A20="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4170,9 +4202,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
-      </c>
-      <c r="G20" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G20" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4180,20 +4212,20 @@
       <c r="A21" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="18" cm="1">
+        <f t="array" ref="E21">_xlfn.IFS(D21="A", 1, D21="B", 2, D21="C", 3, D21="D", 4, TRUE, 0)</f>
         <v>4</v>
       </c>
-      <c r="E21" s="13" cm="1">
-        <f t="array" ref="E21">_xlfn.IFS(D21="A", 1, D21="B", 2, D21="C", 3, D21="D", 4, TRUE, 0)</f>
-        <v>3</v>
-      </c>
-      <c r="F21" s="1" t="str" cm="1">
+      <c r="F21" s="17" t="str" cm="1">
         <f t="array" ref="F21">_xlfn.IFS(
     E21=1, _xlfn.IFS(
         A21="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4216,9 +4248,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REPLATFORM / LIFT-AND-SHAPE</v>
-      </c>
-      <c r="G21" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G21" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4226,20 +4258,20 @@
       <c r="A22" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="13" cm="1">
+      <c r="E22" s="18" cm="1">
         <f t="array" ref="E22">_xlfn.IFS(D22="A", 1, D22="B", 2, D22="C", 3, D22="D", 4, TRUE, 0)</f>
         <v>4</v>
       </c>
-      <c r="F22" s="1" t="str" cm="1">
+      <c r="F22" s="17" t="str" cm="1">
         <f t="array" ref="F22">_xlfn.IFS(
     E22=1, _xlfn.IFS(
         A22="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4264,7 +4296,7 @@
 )</f>
         <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4272,20 +4304,20 @@
       <c r="A23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="13" cm="1">
+      <c r="D23" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="18" cm="1">
         <f t="array" ref="E23">_xlfn.IFS(D23="A", 1, D23="B", 2, D23="C", 3, D23="D", 4, TRUE, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="F23" s="1" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="F23" s="17" t="str" cm="1">
         <f t="array" ref="F23">_xlfn.IFS(
     E23=1, _xlfn.IFS(
         A23="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4308,9 +4340,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
-      </c>
-      <c r="G23" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G23" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4318,20 +4350,20 @@
       <c r="A24" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="18" cm="1">
+        <f t="array" ref="E24">_xlfn.IFS(D24="A", 1, D24="B", 2, D24="C", 3, D24="D", 4, TRUE, 0)</f>
         <v>4</v>
       </c>
-      <c r="E24" s="13" cm="1">
-        <f t="array" ref="E24">_xlfn.IFS(D24="A", 1, D24="B", 2, D24="C", 3, D24="D", 4, TRUE, 0)</f>
-        <v>3</v>
-      </c>
-      <c r="F24" s="1" t="str" cm="1">
+      <c r="F24" s="17" t="str" cm="1">
         <f t="array" ref="F24">_xlfn.IFS(
     E24=1, _xlfn.IFS(
         A24="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4354,9 +4386,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REPLATFORM / LIFT-AND-SHAPE</v>
-      </c>
-      <c r="G24" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G24" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4364,20 +4396,20 @@
       <c r="A25" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="13" cm="1">
+      <c r="D25" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="18" cm="1">
         <f t="array" ref="E25">_xlfn.IFS(D25="A", 1, D25="B", 2, D25="C", 3, D25="D", 4, TRUE, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="F25" s="1" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="F25" s="17" t="str" cm="1">
         <f t="array" ref="F25">_xlfn.IFS(
     E25=1, _xlfn.IFS(
         A25="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4400,9 +4432,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
-      </c>
-      <c r="G25" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G25" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4410,20 +4442,20 @@
       <c r="A26" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="18" cm="1">
+        <f t="array" ref="E26">_xlfn.IFS(D26="A", 1, D26="B", 2, D26="C", 3, D26="D", 4, TRUE, 0)</f>
         <v>4</v>
       </c>
-      <c r="E26" s="13" cm="1">
-        <f t="array" ref="E26">_xlfn.IFS(D26="A", 1, D26="B", 2, D26="C", 3, D26="D", 4, TRUE, 0)</f>
-        <v>3</v>
-      </c>
-      <c r="F26" s="1" t="str" cm="1">
+      <c r="F26" s="17" t="str" cm="1">
         <f t="array" ref="F26">_xlfn.IFS(
     E26=1, _xlfn.IFS(
         A26="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4446,9 +4478,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REPLATFORM / LIFT-AND-SHAPE</v>
-      </c>
-      <c r="G26" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G26" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4456,20 +4488,20 @@
       <c r="A27" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" s="13" cm="1">
+      <c r="D27" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="18" cm="1">
         <f t="array" ref="E27">_xlfn.IFS(D27="A", 1, D27="B", 2, D27="C", 3, D27="D", 4, TRUE, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="F27" s="1" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="F27" s="17" t="str" cm="1">
         <f t="array" ref="F27">_xlfn.IFS(
     E27=1, _xlfn.IFS(
         A27="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4492,9 +4524,9 @@
     ),
     TRUE, ""
 )</f>
-        <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
-      </c>
-      <c r="G27" s="1" t="s">
+        <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
+      </c>
+      <c r="G27" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4502,20 +4534,20 @@
       <c r="A28" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="13" cm="1">
+      <c r="E28" s="18" cm="1">
         <f t="array" ref="E28">_xlfn.IFS(D28="A", 1, D28="B", 2, D28="C", 3, D28="D", 4, TRUE, 0)</f>
         <v>3</v>
       </c>
-      <c r="F28" s="1" t="str" cm="1">
+      <c r="F28" s="17" t="str" cm="1">
         <f t="array" ref="F28">_xlfn.IFS(
     E28=1, _xlfn.IFS(
         A28="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4540,7 +4572,7 @@
 )</f>
         <v>REPLATFORM / LIFT-AND-SHAPE</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4548,20 +4580,20 @@
       <c r="A29" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="13" cm="1">
+      <c r="E29" s="18" cm="1">
         <f t="array" ref="E29">_xlfn.IFS(D29="A", 1, D29="B", 2, D29="C", 3, D29="D", 4, TRUE, 0)</f>
         <v>3</v>
       </c>
-      <c r="F29" s="1" t="str" cm="1">
+      <c r="F29" s="17" t="str" cm="1">
         <f t="array" ref="F29">_xlfn.IFS(
     E29=1, _xlfn.IFS(
         A29="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4586,7 +4618,7 @@
 )</f>
         <v>REPLATFORM / LIFT-AND-SHAPE</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4594,20 +4626,20 @@
       <c r="A30" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E30" s="13" cm="1">
+      <c r="E30" s="18" cm="1">
         <f t="array" ref="E30">_xlfn.IFS(D30="A", 1, D30="B", 2, D30="C", 3, D30="D", 4, TRUE, 0)</f>
         <v>2</v>
       </c>
-      <c r="F30" s="1" t="str" cm="1">
+      <c r="F30" s="17" t="str" cm="1">
         <f t="array" ref="F30">_xlfn.IFS(
     E30=1, _xlfn.IFS(
         A30="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4632,7 +4664,7 @@
 )</f>
         <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4640,20 +4672,20 @@
       <c r="A31" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E31" s="13" cm="1">
+      <c r="E31" s="18" cm="1">
         <f t="array" ref="E31">_xlfn.IFS(D31="A", 1, D31="B", 2, D31="C", 3, D31="D", 4, TRUE, 0)</f>
         <v>2</v>
       </c>
-      <c r="F31" s="1" t="str" cm="1">
+      <c r="F31" s="17" t="str" cm="1">
         <f t="array" ref="F31">_xlfn.IFS(
     E31=1, _xlfn.IFS(
         A31="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4678,7 +4710,7 @@
 )</f>
         <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4686,20 +4718,20 @@
       <c r="A32" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E32" s="13" cm="1">
+      <c r="E32" s="18" cm="1">
         <f t="array" ref="E32">_xlfn.IFS(D32="A", 1, D32="B", 2, D32="C", 3, D32="D", 4, TRUE, 0)</f>
         <v>2</v>
       </c>
-      <c r="F32" s="1" t="str" cm="1">
+      <c r="F32" s="17" t="str" cm="1">
         <f t="array" ref="F32">_xlfn.IFS(
     E32=1, _xlfn.IFS(
         A32="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4724,7 +4756,7 @@
 )</f>
         <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4732,20 +4764,20 @@
       <c r="A33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E33" s="13" cm="1">
+      <c r="E33" s="18" cm="1">
         <f t="array" ref="E33">_xlfn.IFS(D33="A", 1, D33="B", 2, D33="C", 3, D33="D", 4, TRUE, 0)</f>
         <v>2</v>
       </c>
-      <c r="F33" s="1" t="str" cm="1">
+      <c r="F33" s="17" t="str" cm="1">
         <f t="array" ref="F33">_xlfn.IFS(
     E33=1, _xlfn.IFS(
         A33="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4770,7 +4802,7 @@
 )</f>
         <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4778,20 +4810,20 @@
       <c r="A34" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="13" cm="1">
+      <c r="E34" s="18" cm="1">
         <f t="array" ref="E34">_xlfn.IFS(D34="A", 1, D34="B", 2, D34="C", 3, D34="D", 4, TRUE, 0)</f>
         <v>4</v>
       </c>
-      <c r="F34" s="1" t="str" cm="1">
+      <c r="F34" s="17" t="str" cm="1">
         <f t="array" ref="F34">_xlfn.IFS(
     E34=1, _xlfn.IFS(
         A34="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4816,7 +4848,7 @@
 )</f>
         <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4824,20 +4856,20 @@
       <c r="A35" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="13" cm="1">
+      <c r="E35" s="18" cm="1">
         <f t="array" ref="E35">_xlfn.IFS(D35="A", 1, D35="B", 2, D35="C", 3, D35="D", 4, TRUE, 0)</f>
         <v>4</v>
       </c>
-      <c r="F35" s="1" t="str" cm="1">
+      <c r="F35" s="17" t="str" cm="1">
         <f t="array" ref="F35">_xlfn.IFS(
     E35=1, _xlfn.IFS(
         A35="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4862,7 +4894,7 @@
 )</f>
         <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4870,20 +4902,20 @@
       <c r="A36" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E36" s="13" cm="1">
+      <c r="E36" s="18" cm="1">
         <f t="array" ref="E36">_xlfn.IFS(D36="A", 1, D36="B", 2, D36="C", 3, D36="D", 4, TRUE, 0)</f>
         <v>3</v>
       </c>
-      <c r="F36" s="1" t="str" cm="1">
+      <c r="F36" s="17" t="str" cm="1">
         <f t="array" ref="F36">_xlfn.IFS(
     E36=1, _xlfn.IFS(
         A36="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4908,7 +4940,7 @@
 )</f>
         <v>REPLATFORM / LIFT-AND-SHAPE</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4916,20 +4948,20 @@
       <c r="A37" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="13" cm="1">
+      <c r="E37" s="18" cm="1">
         <f t="array" ref="E37">_xlfn.IFS(D37="A", 1, D37="B", 2, D37="C", 3, D37="D", 4, TRUE, 0)</f>
         <v>4</v>
       </c>
-      <c r="F37" s="1" t="str" cm="1">
+      <c r="F37" s="17" t="str" cm="1">
         <f t="array" ref="F37">_xlfn.IFS(
     E37=1, _xlfn.IFS(
         A37="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -4954,7 +4986,7 @@
 )</f>
         <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4962,20 +4994,20 @@
       <c r="A38" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="13" cm="1">
+      <c r="E38" s="18" cm="1">
         <f t="array" ref="E38">_xlfn.IFS(D38="A", 1, D38="B", 2, D38="C", 3, D38="D", 4, TRUE, 0)</f>
         <v>4</v>
       </c>
-      <c r="F38" s="1" t="str" cm="1">
+      <c r="F38" s="17" t="str" cm="1">
         <f t="array" ref="F38">_xlfn.IFS(
     E38=1, _xlfn.IFS(
         A38="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -5000,7 +5032,7 @@
 )</f>
         <v>REHOST (LIFT &amp; SHIFT) (Direct VM Migration Ready)</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5008,20 +5040,20 @@
       <c r="A39" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E39" s="13" cm="1">
+      <c r="E39" s="18" cm="1">
         <f t="array" ref="E39">_xlfn.IFS(D39="A", 1, D39="B", 2, D39="C", 3, D39="D", 4, TRUE, 0)</f>
         <v>2</v>
       </c>
-      <c r="F39" s="1" t="str" cm="1">
+      <c r="F39" s="17" t="str" cm="1">
         <f t="array" ref="F39">_xlfn.IFS(
     E39=1, _xlfn.IFS(
         A39="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -5046,7 +5078,7 @@
 )</f>
         <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5054,20 +5086,20 @@
       <c r="A40" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E40" s="13" cm="1">
+      <c r="E40" s="18" cm="1">
         <f t="array" ref="E40">_xlfn.IFS(D40="A", 1, D40="B", 2, D40="C", 3, D40="D", 4, TRUE, 0)</f>
         <v>2</v>
       </c>
-      <c r="F40" s="1" t="str" cm="1">
+      <c r="F40" s="17" t="str" cm="1">
         <f t="array" ref="F40">_xlfn.IFS(
     E40=1, _xlfn.IFS(
         A40="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -5092,7 +5124,7 @@
 )</f>
         <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5100,20 +5132,20 @@
       <c r="A41" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E41" s="13" cm="1">
+      <c r="E41" s="18" cm="1">
         <f t="array" ref="E41">_xlfn.IFS(D41="A", 1, D41="B", 2, D41="C", 3, D41="D", 4, TRUE, 0)</f>
         <v>2</v>
       </c>
-      <c r="F41" s="1" t="str" cm="1">
+      <c r="F41" s="17" t="str" cm="1">
         <f t="array" ref="F41">_xlfn.IFS(
     E41=1, _xlfn.IFS(
         A41="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -5138,7 +5170,7 @@
 )</f>
         <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5146,20 +5178,20 @@
       <c r="A42" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E42" s="13" cm="1">
+      <c r="E42" s="18" cm="1">
         <f t="array" ref="E42">_xlfn.IFS(D42="A", 1, D42="B", 2, D42="C", 3, D42="D", 4, TRUE, 0)</f>
         <v>2</v>
       </c>
-      <c r="F42" s="1" t="str" cm="1">
+      <c r="F42" s="17" t="str" cm="1">
         <f t="array" ref="F42">_xlfn.IFS(
     E42=1, _xlfn.IFS(
         A42="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -5184,7 +5216,7 @@
 )</f>
         <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5192,20 +5224,20 @@
       <c r="A43" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E43" s="13" cm="1">
+      <c r="E43" s="18" cm="1">
         <f t="array" ref="E43">_xlfn.IFS(D43="A", 1, D43="B", 2, D43="C", 3, D43="D", 4, TRUE, 0)</f>
         <v>2</v>
       </c>
-      <c r="F43" s="1" t="str" cm="1">
+      <c r="F43" s="17" t="str" cm="1">
         <f t="array" ref="F43">_xlfn.IFS(
     E43=1, _xlfn.IFS(
         A43="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -5230,7 +5262,7 @@
 )</f>
         <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5238,20 +5270,20 @@
       <c r="A44" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E44" s="13" cm="1">
+      <c r="E44" s="18" cm="1">
         <f t="array" ref="E44">_xlfn.IFS(D44="A", 1, D44="B", 2, D44="C", 3, D44="D", 4, TRUE, 0)</f>
         <v>2</v>
       </c>
-      <c r="F44" s="1" t="str" cm="1">
+      <c r="F44" s="17" t="str" cm="1">
         <f t="array" ref="F44">_xlfn.IFS(
     E44=1, _xlfn.IFS(
         A44="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -5276,7 +5308,7 @@
 )</f>
         <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5284,20 +5316,20 @@
       <c r="A45" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E45" s="13" cm="1">
+      <c r="E45" s="18" cm="1">
         <f t="array" ref="E45">_xlfn.IFS(D45="A", 1, D45="B", 2, D45="C", 3, D45="D", 4, TRUE, 0)</f>
         <v>3</v>
       </c>
-      <c r="F45" s="1" t="str" cm="1">
+      <c r="F45" s="17" t="str" cm="1">
         <f t="array" ref="F45">_xlfn.IFS(
     E45=1, _xlfn.IFS(
         A45="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -5322,7 +5354,7 @@
 )</f>
         <v>REPLATFORM / LIFT-AND-SHAPE</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5330,20 +5362,20 @@
       <c r="A46" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E46" s="13" cm="1">
+      <c r="E46" s="18" cm="1">
         <f t="array" ref="E46">_xlfn.IFS(D46="A", 1, D46="B", 2, D46="C", 3, D46="D", 4, TRUE, 0)</f>
         <v>2</v>
       </c>
-      <c r="F46" s="1" t="str" cm="1">
+      <c r="F46" s="17" t="str" cm="1">
         <f t="array" ref="F46">_xlfn.IFS(
     E46=1, _xlfn.IFS(
         A46="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -5368,7 +5400,7 @@
 )</f>
         <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5376,20 +5408,20 @@
       <c r="A47" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E47" s="13" cm="1">
+      <c r="E47" s="18" cm="1">
         <f t="array" ref="E47">_xlfn.IFS(D47="A", 1, D47="B", 2, D47="C", 3, D47="D", 4, TRUE, 0)</f>
         <v>2</v>
       </c>
-      <c r="F47" s="1" t="str" cm="1">
+      <c r="F47" s="17" t="str" cm="1">
         <f t="array" ref="F47">_xlfn.IFS(
     E47=1, _xlfn.IFS(
         A47="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -5414,7 +5446,7 @@
 )</f>
         <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5422,20 +5454,20 @@
       <c r="A48" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E48" s="13" cm="1">
+      <c r="E48" s="18" cm="1">
         <f t="array" ref="E48">_xlfn.IFS(D48="A", 1, D48="B", 2, D48="C", 3, D48="D", 4, TRUE, 0)</f>
         <v>2</v>
       </c>
-      <c r="F48" s="1" t="str" cm="1">
+      <c r="F48" s="17" t="str" cm="1">
         <f t="array" ref="F48">_xlfn.IFS(
     E48=1, _xlfn.IFS(
         A48="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -5460,7 +5492,7 @@
 )</f>
         <v>REFACTOR / RE-ARCHITECT (High Migration Debt)</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5468,20 +5500,20 @@
       <c r="A49" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="11" t="s">
         <v>111</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E49" s="13" cm="1">
+      <c r="E49" s="18" cm="1">
         <f t="array" ref="E49">_xlfn.IFS(D49="A", 1, D49="B", 2, D49="C", 3, D49="D", 4, TRUE, 0)</f>
         <v>1</v>
       </c>
-      <c r="F49" s="1" t="str" cm="1">
+      <c r="F49" s="17" t="str" cm="1">
         <f t="array" ref="F49">_xlfn.IFS(
     E49=1, _xlfn.IFS(
         A49="Security, Identity &amp; Compliance", "RETAIN (Critical Legal/Sovereignty Roadblock)",
@@ -5506,29 +5538,32 @@
 )</f>
         <v>RETAIN (Fatal System/Dependency Blocker)</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="15" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B50" s="10"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B51" s="10"/>
+      <c r="B50" s="9"/>
+    </row>
+    <row r="51" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B51" s="12" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B52" s="10"/>
+      <c r="B52" s="9"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B53" s="10"/>
+      <c r="B53" s="9"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B54" s="10"/>
+      <c r="B54" s="9"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B55" s="10"/>
+      <c r="B55" s="9"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="9kp5B8sHnQ8Ir/yRRw5iMR8PFsdcUjkHc8eJReQvQcW5ilG3S9RMrosjQAbqQmWKJ6x/s2q/Hd7kTycdc8in+A==" saltValue="Y3dj56F8zSSwW4GHQNjPRQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataValidations xWindow="1300" yWindow="864" count="3">
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Choice" error="You must select a letter from the dropdown list (A, B, C, or D)" promptTitle="Select Maturity" prompt="Please select an option from A to D based on your team's current operations" sqref="D2:D9 D17" xr:uid="{509BDBE0-139A-45CF-85F3-A20E0266477C}">
       <formula1>"A,B,C,D"</formula1>
@@ -5551,7 +5586,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00DD14C9-A019-4A4F-9EC1-2104829600EF}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="60.109375" customWidth="1"/>
@@ -5560,10 +5595,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -5574,43 +5609,43 @@
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="19">
         <f>AVERAGEIF(Inputs!A:A, A2, Inputs!E:E)</f>
-        <v>2.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="19">
         <f>AVERAGEIF(Inputs!A:A, A3, Inputs!E:E)</f>
-        <v>2.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="19">
         <f>AVERAGEIF(Inputs!A:A, A4, Inputs!E:E)</f>
-        <v>2.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="19">
         <f>AVERAGEIF(Inputs!A:A, A5, Inputs!E:E)</f>
-        <v>2.375</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="19">
         <f>AVERAGEIF(Inputs!A:A, A6, Inputs!E:E)</f>
         <v>3.125</v>
       </c>
@@ -5619,18 +5654,18 @@
       <c r="A7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="19">
         <f>AVERAGEIF(Inputs!A:A, A7, Inputs!E:E)</f>
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="58.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C9" s="1" t="str" cm="1">
+      <c r="C9" s="17" t="str" cm="1">
         <f t="array" ref="C9">_xlfn.IFS(
     COUNTIF(Inputs!E2:E48, 1) &gt; 12,
     "STRATEGY: MULTI-TIER RETAIN &amp; RETIRE BLOCK (Portfolio exhibits terminal technical debt. Immediate freeze.)",
@@ -5647,104 +5682,110 @@
     TRUE,
     "STRATEGY: COMPLETE REPURCHASE (Workload is severely unoptimized for cloud IaaS. Decommission internal code and procure a standard third-party SaaS alternative.)"
 )</f>
-        <v>STRATEGY: HYBRID RETAIN (Workload is cloud-compatible but blocked by localized Compliance or Data Sovereignty mandates.)</v>
+        <v>STRATEGY: CORE REHOST (Workload runtime profiles are stable and standard. Deploy automated replication agents for a rapid Lift-and-Shift.)</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="C11" s="6"/>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="27" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="13" t="s">
+        <v>120</v>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="eXyTsItH3MtNMNeN9ICTVEuYgKVMS6yNHubFm+NfAaDhK/+sRA57ztLhS3IRdOSasvmh560g7CNLmdBXRYAm4w==" saltValue="mKpCs5QV0Mf+G2F6oRhKCQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <conditionalFormatting sqref="B10">
-    <cfRule type="containsText" dxfId="29" priority="61" stopIfTrue="1" operator="containsText" text="STATE 15">
+    <cfRule type="containsText" dxfId="33" priority="61" stopIfTrue="1" operator="containsText" text="STATE 15">
       <formula>NOT(ISERROR(SEARCH("STATE 15",B10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="62" stopIfTrue="1" operator="containsText" text="STATE 14:">
+    <cfRule type="containsText" dxfId="32" priority="62" stopIfTrue="1" operator="containsText" text="STATE 14:">
       <formula>NOT(ISERROR(SEARCH("STATE 14:",B10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="63" stopIfTrue="1" operator="containsText" text="STATE 13:">
+    <cfRule type="containsText" dxfId="31" priority="63" stopIfTrue="1" operator="containsText" text="STATE 13:">
       <formula>NOT(ISERROR(SEARCH("STATE 13:",B10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="64" stopIfTrue="1" operator="containsText" text="STATE 12:">
+    <cfRule type="containsText" dxfId="30" priority="64" stopIfTrue="1" operator="containsText" text="STATE 12:">
       <formula>NOT(ISERROR(SEARCH("STATE 12:",B10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="65" stopIfTrue="1" operator="containsText" text="STATE 11:">
+    <cfRule type="containsText" dxfId="29" priority="65" stopIfTrue="1" operator="containsText" text="STATE 11:">
       <formula>NOT(ISERROR(SEARCH("STATE 11:",B10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="66" stopIfTrue="1" operator="containsText" text="STATE 10:">
+    <cfRule type="containsText" dxfId="28" priority="66" stopIfTrue="1" operator="containsText" text="STATE 10:">
       <formula>NOT(ISERROR(SEARCH("STATE 10:",B10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="67" stopIfTrue="1" operator="containsText" text="STATE 9:">
+    <cfRule type="containsText" dxfId="27" priority="67" stopIfTrue="1" operator="containsText" text="STATE 9:">
       <formula>NOT(ISERROR(SEARCH("STATE 9:",B10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="68" stopIfTrue="1" operator="containsText" text="STATE 8:">
+    <cfRule type="containsText" dxfId="26" priority="68" stopIfTrue="1" operator="containsText" text="STATE 8:">
       <formula>NOT(ISERROR(SEARCH("STATE 8:",B10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="69" stopIfTrue="1" operator="containsText" text="STATE 7:">
+    <cfRule type="containsText" dxfId="25" priority="69" stopIfTrue="1" operator="containsText" text="STATE 7:">
       <formula>NOT(ISERROR(SEARCH("STATE 7:",B10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="70" stopIfTrue="1" operator="containsText" text="STATE 6:">
+    <cfRule type="containsText" dxfId="24" priority="70" stopIfTrue="1" operator="containsText" text="STATE 6:">
       <formula>NOT(ISERROR(SEARCH("STATE 6:",B10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="71" stopIfTrue="1" operator="containsText" text="STATE 5:">
+    <cfRule type="containsText" dxfId="23" priority="71" stopIfTrue="1" operator="containsText" text="STATE 5:">
       <formula>NOT(ISERROR(SEARCH("STATE 5:",B10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="72" stopIfTrue="1" operator="containsText" text="STATE 4:">
+    <cfRule type="containsText" dxfId="22" priority="72" stopIfTrue="1" operator="containsText" text="STATE 4:">
       <formula>NOT(ISERROR(SEARCH("STATE 4:",B10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="73" stopIfTrue="1" operator="containsText" text="STATE 3:">
+    <cfRule type="containsText" dxfId="21" priority="73" stopIfTrue="1" operator="containsText" text="STATE 3:">
       <formula>NOT(ISERROR(SEARCH("STATE 3:",B10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="74" stopIfTrue="1" operator="containsText" text="STATE 2:">
+    <cfRule type="containsText" dxfId="20" priority="74" stopIfTrue="1" operator="containsText" text="STATE 2:">
       <formula>NOT(ISERROR(SEARCH("STATE 2:",B10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="75" stopIfTrue="1" operator="containsText" text="STATE 1:">
+    <cfRule type="containsText" dxfId="19" priority="75" stopIfTrue="1" operator="containsText" text="STATE 1:">
       <formula>NOT(ISERROR(SEARCH("STATE 1:",B10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="containsText" dxfId="14" priority="1" stopIfTrue="1" operator="containsText" text="STATE 15">
+    <cfRule type="containsText" dxfId="18" priority="1" stopIfTrue="1" operator="containsText" text="STATE 15">
       <formula>NOT(ISERROR(SEARCH("STATE 15",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="2" stopIfTrue="1" operator="containsText" text="STATE 14:">
+    <cfRule type="containsText" dxfId="17" priority="2" stopIfTrue="1" operator="containsText" text="STATE 14:">
       <formula>NOT(ISERROR(SEARCH("STATE 14:",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="3" stopIfTrue="1" operator="containsText" text="STATE 13:">
+    <cfRule type="containsText" dxfId="16" priority="3" stopIfTrue="1" operator="containsText" text="STATE 13:">
       <formula>NOT(ISERROR(SEARCH("STATE 13:",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="4" stopIfTrue="1" operator="containsText" text="STATE 12:">
+    <cfRule type="containsText" dxfId="15" priority="4" stopIfTrue="1" operator="containsText" text="STATE 12:">
       <formula>NOT(ISERROR(SEARCH("STATE 12:",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="5" stopIfTrue="1" operator="containsText" text="STATE 11:">
+    <cfRule type="containsText" dxfId="14" priority="5" stopIfTrue="1" operator="containsText" text="STATE 11:">
       <formula>NOT(ISERROR(SEARCH("STATE 11:",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="6" stopIfTrue="1" operator="containsText" text="STATE 10:">
+    <cfRule type="containsText" dxfId="13" priority="6" stopIfTrue="1" operator="containsText" text="STATE 10:">
       <formula>NOT(ISERROR(SEARCH("STATE 10:",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="7" stopIfTrue="1" operator="containsText" text="STATE 9:">
+    <cfRule type="containsText" dxfId="12" priority="7" stopIfTrue="1" operator="containsText" text="STATE 9:">
       <formula>NOT(ISERROR(SEARCH("STATE 9:",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="8" stopIfTrue="1" operator="containsText" text="STATE 8:">
+    <cfRule type="containsText" dxfId="11" priority="8" stopIfTrue="1" operator="containsText" text="STATE 8:">
       <formula>NOT(ISERROR(SEARCH("STATE 8:",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="9" stopIfTrue="1" operator="containsText" text="STATE 7:">
+    <cfRule type="containsText" dxfId="10" priority="9" stopIfTrue="1" operator="containsText" text="STATE 7:">
       <formula>NOT(ISERROR(SEARCH("STATE 7:",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="10" stopIfTrue="1" operator="containsText" text="STATE 6:">
+    <cfRule type="containsText" dxfId="9" priority="10" stopIfTrue="1" operator="containsText" text="STATE 6:">
       <formula>NOT(ISERROR(SEARCH("STATE 6:",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="11" stopIfTrue="1" operator="containsText" text="STATE 5:">
+    <cfRule type="containsText" dxfId="8" priority="11" stopIfTrue="1" operator="containsText" text="STATE 5:">
       <formula>NOT(ISERROR(SEARCH("STATE 5:",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="12" stopIfTrue="1" operator="containsText" text="STATE 4:">
+    <cfRule type="containsText" dxfId="7" priority="12" stopIfTrue="1" operator="containsText" text="STATE 4:">
       <formula>NOT(ISERROR(SEARCH("STATE 4:",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="13" stopIfTrue="1" operator="containsText" text="STATE 3:">
+    <cfRule type="containsText" dxfId="6" priority="13" stopIfTrue="1" operator="containsText" text="STATE 3:">
       <formula>NOT(ISERROR(SEARCH("STATE 3:",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="14" stopIfTrue="1" operator="containsText" text="STATE 2:">
+    <cfRule type="containsText" dxfId="5" priority="14" stopIfTrue="1" operator="containsText" text="STATE 2:">
       <formula>NOT(ISERROR(SEARCH("STATE 2:",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" stopIfTrue="1" operator="containsText" text="STATE 1:">
+    <cfRule type="containsText" dxfId="4" priority="15" stopIfTrue="1" operator="containsText" text="STATE 1:">
       <formula>NOT(ISERROR(SEARCH("STATE 1:",C9)))</formula>
     </cfRule>
   </conditionalFormatting>
